--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0004.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0004.xlsx
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Fler vargar</t>
+          <t>Gårdarna blev större</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Färre städer</t>
+          <t>Arbetet rationaliserades</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Mindre handel</t>
+          <t>Färre behövdes i jordbruket</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Till Antarktis</t>
+          <t>Till industristäder i södra Finland</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Till öde öar</t>
+          <t>Till andra delar av Finland</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Till Lappland enbart</t>
+          <t>Till Sverige</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Bara jordbruk</t>
+          <t>Främst jordbruk</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Bara fiske</t>
+          <t>Främst fiske</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Bara gruvor</t>
+          <t>Främst gruvdrift</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Den var bara för rika</t>
+          <t>Den var främst för elever med höga betyg</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Den skulle vara 3-årig</t>
+          <t>Den skulle vara 6-årig</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Den skulle ersätta all utbildning</t>
+          <t>Den skulle delas upp tidigt i olika linjer</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Det fanns för många jobb</t>
+          <t>Högre löner utomlands</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Skatter var noll</t>
+          <t>Efterfrågan på arbetskraft i Sverige</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Alla ville bli turister</t>
+          <t>Bättre karriärmöjligheter</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Över 40 000</t>
+          <t>Över 200 000</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Över 4 000 000</t>
+          <t>Över 600 000</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Över 4 000</t>
+          <t>Över 800 000</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Sverige stängde skolor</t>
+          <t>De hade sparat ihop pengar</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>EU förbjöd migration</t>
+          <t>Familjeskäl</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Finland blev koloni</t>
+          <t>De ville återvända efter några år</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>De flyttade alla till Norge</t>
+          <t>De fick jobb och bostad i Sverige</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>De flyttade alla till USA</t>
+          <t>De bildade familj i Sverige</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>De flyttade alla till Finland direkt</t>
+          <t>De flyttade vidare till andra länder</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Norrmän</t>
+          <t>Jugoslaver</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Tyskar</t>
+          <t>Irakier</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Japaner</t>
+          <t>Polacker</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Helt identiskt</t>
+          <t>Ganska likt Sverige</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Utan industri alls i Sverige</t>
+          <t>Mer jordbruksdominerat än Sverige</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Brutna handelsavtal med EU</t>
+          <t>Sen industrialisering</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>För många universitet</t>
+          <t>Lägre produktivitet</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>För lite skog</t>
+          <t>Svagare exportindustri</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Den avskaffades</t>
+          <t>Den ökade främst i vissa grupper</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Bara bröd och vatten</t>
+          <t>Det nödvändigaste</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Ingenting alls</t>
+          <t>Ungefär lika mycket som tidigare</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Endast ved</t>
+          <t>Mindre än tidigare på grund av inflation</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Mjölkpriser i hela världen</t>
+          <t>Räntor</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Priser på snö</t>
+          <t>Aktiepriser</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Priser på luft</t>
+          <t>Lönenivåer</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Den var helt stabil</t>
+          <t>Den var relativt stabil</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Den stängdes av</t>
+          <t>Den växte långsamt</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Den blev helt statlig</t>
+          <t>Den bromsade in gradvis</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Ingen arbetslöshet</t>
+          <t>Hög inflation</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Noll konkurs</t>
+          <t>Stigande räntor</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Gratis bostäder</t>
+          <t>Minskad export</t>
         </is>
       </c>
       <c r="G28" s="14" t="n">
